--- a/data_lake/datos_diarios_preliminares/dt=2026-07-12/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-12/temperaturamed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{940501FD-3AF0-4B39-95BD-C7022BF5373A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96D3E4FC-8736-4DE2-9ED1-28D3D3682EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6347,8 +6347,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="97" width="32.42578125" style="50" customWidth="1"/>
-    <col min="98" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="98" width="32.42578125" style="50" customWidth="1"/>
+    <col min="99" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6661,7 +6661,9 @@
       <c r="T5" s="56">
         <v>29.1</v>
       </c>
-      <c r="U5" s="56"/>
+      <c r="U5" s="56">
+        <v>29.8</v>
+      </c>
       <c r="V5" s="56"/>
       <c r="W5" s="56"/>
       <c r="X5" s="56"/>
@@ -6684,7 +6686,7 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ5" s="71" t="str">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
@@ -6760,7 +6762,9 @@
       <c r="T6" s="56">
         <v>28.7</v>
       </c>
-      <c r="U6" s="56"/>
+      <c r="U6" s="56">
+        <v>29.1</v>
+      </c>
       <c r="V6" s="56"/>
       <c r="W6" s="56"/>
       <c r="X6" s="56"/>
@@ -6783,7 +6787,7 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ6" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6859,7 +6863,9 @@
       <c r="T7" s="56">
         <v>30.2</v>
       </c>
-      <c r="U7" s="56"/>
+      <c r="U7" s="56">
+        <v>32</v>
+      </c>
       <c r="V7" s="56"/>
       <c r="W7" s="56"/>
       <c r="X7" s="56"/>
@@ -6882,7 +6888,7 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6958,7 +6964,9 @@
       <c r="T8" s="56">
         <v>30.1</v>
       </c>
-      <c r="U8" s="56"/>
+      <c r="U8" s="56">
+        <v>30.5</v>
+      </c>
       <c r="V8" s="56"/>
       <c r="W8" s="56"/>
       <c r="X8" s="56"/>
@@ -6981,7 +6989,7 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ8" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7057,7 +7065,9 @@
       <c r="T9" s="56">
         <v>29.1</v>
       </c>
-      <c r="U9" s="56"/>
+      <c r="U9" s="56">
+        <v>29.7</v>
+      </c>
       <c r="V9" s="56"/>
       <c r="W9" s="56"/>
       <c r="X9" s="56"/>
@@ -7080,7 +7090,7 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ9" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7156,7 +7166,9 @@
       <c r="T10" s="56">
         <v>31.1</v>
       </c>
-      <c r="U10" s="56"/>
+      <c r="U10" s="56">
+        <v>30.7</v>
+      </c>
       <c r="V10" s="56"/>
       <c r="W10" s="56"/>
       <c r="X10" s="56"/>
@@ -7179,7 +7191,7 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ10" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7255,7 +7267,9 @@
       <c r="T11" s="56">
         <v>33.1</v>
       </c>
-      <c r="U11" s="56"/>
+      <c r="U11" s="56">
+        <v>33.5</v>
+      </c>
       <c r="V11" s="56"/>
       <c r="W11" s="56"/>
       <c r="X11" s="56"/>
@@ -7278,7 +7292,7 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ11" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7354,7 +7368,9 @@
       <c r="T12" s="56">
         <v>30.9</v>
       </c>
-      <c r="U12" s="56"/>
+      <c r="U12" s="56">
+        <v>30.7</v>
+      </c>
       <c r="V12" s="56"/>
       <c r="W12" s="56"/>
       <c r="X12" s="56"/>
@@ -7377,7 +7393,7 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ12" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7453,7 +7469,9 @@
       <c r="T13" s="56">
         <v>29.7</v>
       </c>
-      <c r="U13" s="56"/>
+      <c r="U13" s="56">
+        <v>30.3</v>
+      </c>
       <c r="V13" s="56"/>
       <c r="W13" s="56"/>
       <c r="X13" s="56"/>
@@ -7476,7 +7494,7 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ13" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7552,7 +7570,9 @@
       <c r="T14" s="56">
         <v>23.2</v>
       </c>
-      <c r="U14" s="56"/>
+      <c r="U14" s="56">
+        <v>23.7</v>
+      </c>
       <c r="V14" s="56"/>
       <c r="W14" s="56"/>
       <c r="X14" s="56"/>
@@ -7575,7 +7595,7 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ14" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7651,7 +7671,9 @@
       <c r="T15" s="56">
         <v>30.5</v>
       </c>
-      <c r="U15" s="56"/>
+      <c r="U15" s="56">
+        <v>29</v>
+      </c>
       <c r="V15" s="56"/>
       <c r="W15" s="56"/>
       <c r="X15" s="56"/>
@@ -7674,7 +7696,7 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ15" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7750,7 +7772,9 @@
       <c r="T16" s="56">
         <v>28.9</v>
       </c>
-      <c r="U16" s="56"/>
+      <c r="U16" s="56">
+        <v>27.5</v>
+      </c>
       <c r="V16" s="56"/>
       <c r="W16" s="56"/>
       <c r="X16" s="56"/>
@@ -7773,7 +7797,7 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ16" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7849,7 +7873,9 @@
       <c r="T17" s="56">
         <v>25.8</v>
       </c>
-      <c r="U17" s="56"/>
+      <c r="U17" s="56">
+        <v>25.4</v>
+      </c>
       <c r="V17" s="56"/>
       <c r="W17" s="56"/>
       <c r="X17" s="56"/>
@@ -7872,7 +7898,7 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7948,7 +7974,9 @@
       <c r="T18" s="56">
         <v>18.5</v>
       </c>
-      <c r="U18" s="56"/>
+      <c r="U18" s="56">
+        <v>18.7</v>
+      </c>
       <c r="V18" s="56"/>
       <c r="W18" s="56"/>
       <c r="X18" s="56"/>
@@ -7971,7 +7999,7 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ18" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8047,7 +8075,9 @@
       <c r="T19" s="56">
         <v>25.2</v>
       </c>
-      <c r="U19" s="56"/>
+      <c r="U19" s="56">
+        <v>24.2</v>
+      </c>
       <c r="V19" s="56"/>
       <c r="W19" s="56"/>
       <c r="X19" s="56"/>
@@ -8070,7 +8100,7 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ19" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8146,7 +8176,9 @@
       <c r="T20" s="56">
         <v>26.3</v>
       </c>
-      <c r="U20" s="56"/>
+      <c r="U20" s="56">
+        <v>23.6</v>
+      </c>
       <c r="V20" s="56"/>
       <c r="W20" s="56"/>
       <c r="X20" s="56"/>
@@ -8169,7 +8201,7 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ20" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8245,7 +8277,9 @@
       <c r="T21" s="56">
         <v>26</v>
       </c>
-      <c r="U21" s="56"/>
+      <c r="U21" s="56">
+        <v>27.3</v>
+      </c>
       <c r="V21" s="56"/>
       <c r="W21" s="56"/>
       <c r="X21" s="56"/>
@@ -8268,7 +8302,7 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ21" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8344,7 +8378,9 @@
       <c r="T22" s="56">
         <v>15.8</v>
       </c>
-      <c r="U22" s="56"/>
+      <c r="U22" s="56">
+        <v>14.5</v>
+      </c>
       <c r="V22" s="56"/>
       <c r="W22" s="56"/>
       <c r="X22" s="56"/>
@@ -8367,7 +8403,7 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ22" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8443,7 +8479,9 @@
       <c r="T23" s="56">
         <v>26.5</v>
       </c>
-      <c r="U23" s="56"/>
+      <c r="U23" s="56">
+        <v>25.9</v>
+      </c>
       <c r="V23" s="56"/>
       <c r="W23" s="56"/>
       <c r="X23" s="56"/>
@@ -8466,7 +8504,7 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ23" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8542,7 +8580,9 @@
       <c r="T24" s="56">
         <v>29.1</v>
       </c>
-      <c r="U24" s="56"/>
+      <c r="U24" s="56">
+        <v>30.1</v>
+      </c>
       <c r="V24" s="56"/>
       <c r="W24" s="56"/>
       <c r="X24" s="56"/>
@@ -8565,7 +8605,7 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ24" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8641,7 +8681,9 @@
       <c r="T25" s="56">
         <v>23.1</v>
       </c>
-      <c r="U25" s="56"/>
+      <c r="U25" s="56">
+        <v>21</v>
+      </c>
       <c r="V25" s="56"/>
       <c r="W25" s="56"/>
       <c r="X25" s="56"/>
@@ -8664,7 +8706,7 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ25" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8740,7 +8782,9 @@
       <c r="T26" s="56">
         <v>11.6</v>
       </c>
-      <c r="U26" s="56"/>
+      <c r="U26" s="56">
+        <v>11.7</v>
+      </c>
       <c r="V26" s="56"/>
       <c r="W26" s="56"/>
       <c r="X26" s="56"/>
@@ -8763,7 +8807,7 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ26" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8839,7 +8883,9 @@
       <c r="T27" s="56">
         <v>27.5</v>
       </c>
-      <c r="U27" s="56"/>
+      <c r="U27" s="56">
+        <v>27.9</v>
+      </c>
       <c r="V27" s="56"/>
       <c r="W27" s="56"/>
       <c r="X27" s="56"/>
@@ -8862,7 +8908,7 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ27" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8938,7 +8984,9 @@
       <c r="T28" s="56">
         <v>25.1</v>
       </c>
-      <c r="U28" s="56"/>
+      <c r="U28" s="56">
+        <v>26.3</v>
+      </c>
       <c r="V28" s="56"/>
       <c r="W28" s="56"/>
       <c r="X28" s="56"/>
@@ -8961,7 +9009,7 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ28" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9037,7 +9085,9 @@
       <c r="T29" s="56">
         <v>25.6</v>
       </c>
-      <c r="U29" s="56"/>
+      <c r="U29" s="56">
+        <v>28.9</v>
+      </c>
       <c r="V29" s="56"/>
       <c r="W29" s="56"/>
       <c r="X29" s="56"/>
@@ -9060,7 +9110,7 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ29" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9136,7 +9186,9 @@
       <c r="T30" s="56">
         <v>25.6</v>
       </c>
-      <c r="U30" s="56"/>
+      <c r="U30" s="56">
+        <v>25.9</v>
+      </c>
       <c r="V30" s="56"/>
       <c r="W30" s="56"/>
       <c r="X30" s="56"/>
@@ -9159,7 +9211,7 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ30" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9235,7 +9287,9 @@
       <c r="T31" s="98">
         <v>27</v>
       </c>
-      <c r="U31" s="98"/>
+      <c r="U31" s="98">
+        <v>24.9</v>
+      </c>
       <c r="V31" s="98"/>
       <c r="W31" s="98"/>
       <c r="X31" s="98"/>
@@ -9258,7 +9312,7 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ31" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9334,7 +9388,9 @@
       <c r="T32" s="56">
         <v>21.06666666666667</v>
       </c>
-      <c r="U32" s="56"/>
+      <c r="U32" s="56">
+        <v>20.8</v>
+      </c>
       <c r="V32" s="56"/>
       <c r="W32" s="56"/>
       <c r="X32" s="56"/>
@@ -9357,7 +9413,7 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ32" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9433,7 +9489,9 @@
       <c r="T33" s="56">
         <v>28.7</v>
       </c>
-      <c r="U33" s="56"/>
+      <c r="U33" s="56">
+        <v>26.85</v>
+      </c>
       <c r="V33" s="56"/>
       <c r="W33" s="56"/>
       <c r="X33" s="56"/>
@@ -9456,7 +9514,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9631,7 +9689,9 @@
       <c r="T35" s="56">
         <v>24.15</v>
       </c>
-      <c r="U35" s="56"/>
+      <c r="U35" s="56">
+        <v>23.65</v>
+      </c>
       <c r="V35" s="56"/>
       <c r="W35" s="56"/>
       <c r="X35" s="56"/>
@@ -9654,7 +9714,7 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ35" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9730,7 +9790,9 @@
       <c r="T36" s="56">
         <v>20.65</v>
       </c>
-      <c r="U36" s="56"/>
+      <c r="U36" s="56">
+        <v>20.2</v>
+      </c>
       <c r="V36" s="56"/>
       <c r="W36" s="56"/>
       <c r="X36" s="56"/>
@@ -9753,7 +9815,7 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ36" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9829,7 +9891,9 @@
       <c r="T37" s="56">
         <v>28.9</v>
       </c>
-      <c r="U37" s="56"/>
+      <c r="U37" s="56">
+        <v>26.75</v>
+      </c>
       <c r="V37" s="56"/>
       <c r="W37" s="56"/>
       <c r="X37" s="56"/>
@@ -9852,7 +9916,7 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ37" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9928,7 +9992,9 @@
       <c r="T38" s="56">
         <v>16.7</v>
       </c>
-      <c r="U38" s="56"/>
+      <c r="U38" s="56">
+        <v>15.4</v>
+      </c>
       <c r="V38" s="56"/>
       <c r="W38" s="56"/>
       <c r="X38" s="56"/>
@@ -9951,7 +10017,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10027,7 +10093,9 @@
       <c r="T39" s="56">
         <v>23.13333333333334</v>
       </c>
-      <c r="U39" s="56"/>
+      <c r="U39" s="56">
+        <v>21.733333333333331</v>
+      </c>
       <c r="V39" s="56"/>
       <c r="W39" s="56"/>
       <c r="X39" s="56"/>
@@ -10050,7 +10118,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10124,7 +10192,9 @@
       <c r="T40" s="56">
         <v>25.466666666666669</v>
       </c>
-      <c r="U40" s="56"/>
+      <c r="U40" s="56">
+        <v>25.06666666666667</v>
+      </c>
       <c r="V40" s="56"/>
       <c r="W40" s="56"/>
       <c r="X40" s="56"/>
@@ -10147,7 +10217,7 @@
       <c r="AO40" s="56"/>
       <c r="AP40" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ40" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10223,7 +10293,9 @@
       <c r="T41" s="56">
         <v>21.6</v>
       </c>
-      <c r="U41" s="56"/>
+      <c r="U41" s="56">
+        <v>19.600000000000001</v>
+      </c>
       <c r="V41" s="56"/>
       <c r="W41" s="56"/>
       <c r="X41" s="56"/>
@@ -10246,7 +10318,7 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ41" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10322,7 +10394,9 @@
       <c r="T42" s="56">
         <v>28.15</v>
       </c>
-      <c r="U42" s="56"/>
+      <c r="U42" s="56">
+        <v>28.6</v>
+      </c>
       <c r="V42" s="56"/>
       <c r="W42" s="56"/>
       <c r="X42" s="56"/>
@@ -10345,7 +10419,7 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ42" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10417,7 +10491,9 @@
       <c r="T43" s="56">
         <v>28.75</v>
       </c>
-      <c r="U43" s="56"/>
+      <c r="U43" s="56">
+        <v>29.85</v>
+      </c>
       <c r="V43" s="56"/>
       <c r="W43" s="56"/>
       <c r="X43" s="56"/>
@@ -10440,7 +10516,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10516,7 +10592,9 @@
       <c r="T44" s="56">
         <v>28.8</v>
       </c>
-      <c r="U44" s="56"/>
+      <c r="U44" s="56">
+        <v>29.45</v>
+      </c>
       <c r="V44" s="56"/>
       <c r="W44" s="56"/>
       <c r="X44" s="56"/>
@@ -10539,7 +10617,7 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ44" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10615,7 +10693,9 @@
       <c r="T45" s="56">
         <v>28.6</v>
       </c>
-      <c r="U45" s="56"/>
+      <c r="U45" s="56">
+        <v>28.8</v>
+      </c>
       <c r="V45" s="56"/>
       <c r="W45" s="56"/>
       <c r="X45" s="56"/>
@@ -10638,7 +10718,7 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ45" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10714,7 +10794,9 @@
       <c r="T46" s="56">
         <v>29.86666666666666</v>
       </c>
-      <c r="U46" s="56"/>
+      <c r="U46" s="56">
+        <v>30.333333333333329</v>
+      </c>
       <c r="V46" s="56"/>
       <c r="W46" s="56"/>
       <c r="X46" s="56"/>
@@ -10737,7 +10819,7 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ46" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10971,7 +11053,9 @@
       <c r="T49" s="56">
         <v>29.15</v>
       </c>
-      <c r="U49" s="56"/>
+      <c r="U49" s="56">
+        <v>30.9</v>
+      </c>
       <c r="V49" s="56"/>
       <c r="W49" s="56"/>
       <c r="X49" s="56"/>
@@ -10994,7 +11078,7 @@
       <c r="AO49" s="56"/>
       <c r="AP49" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ49" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11070,7 +11154,9 @@
       <c r="T50" s="56">
         <v>29.4</v>
       </c>
-      <c r="U50" s="56"/>
+      <c r="U50" s="56">
+        <v>29.9</v>
+      </c>
       <c r="V50" s="56"/>
       <c r="W50" s="56"/>
       <c r="X50" s="56"/>
@@ -11093,7 +11179,7 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ50" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11248,7 +11334,9 @@
       <c r="T52" s="56">
         <v>29.35</v>
       </c>
-      <c r="U52" s="56"/>
+      <c r="U52" s="56">
+        <v>29.6</v>
+      </c>
       <c r="V52" s="56"/>
       <c r="W52" s="56"/>
       <c r="X52" s="56"/>
@@ -11271,7 +11359,7 @@
       <c r="AO52" s="56"/>
       <c r="AP52" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ52" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11347,7 +11435,9 @@
       <c r="T53" s="56">
         <v>30.1</v>
       </c>
-      <c r="U53" s="56"/>
+      <c r="U53" s="56">
+        <v>30.1</v>
+      </c>
       <c r="V53" s="56"/>
       <c r="W53" s="56"/>
       <c r="X53" s="56"/>
@@ -11370,7 +11460,7 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11434,7 +11524,9 @@
       <c r="T54" s="56">
         <v>31.8</v>
       </c>
-      <c r="U54" s="56"/>
+      <c r="U54" s="56">
+        <v>30.5</v>
+      </c>
       <c r="V54" s="56"/>
       <c r="W54" s="56"/>
       <c r="X54" s="56"/>
@@ -11457,7 +11549,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11790,7 +11882,9 @@
       <c r="T58" s="56">
         <v>30.4</v>
       </c>
-      <c r="U58" s="56"/>
+      <c r="U58" s="56">
+        <v>29.1</v>
+      </c>
       <c r="V58" s="56"/>
       <c r="W58" s="56"/>
       <c r="X58" s="56"/>
@@ -11813,7 +11907,7 @@
       <c r="AO58" s="56"/>
       <c r="AP58" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ58" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12081,7 +12175,9 @@
       <c r="T61" s="56">
         <v>26.06666666666667</v>
       </c>
-      <c r="U61" s="56"/>
+      <c r="U61" s="56">
+        <v>25.533333333333331</v>
+      </c>
       <c r="V61" s="56"/>
       <c r="W61" s="56"/>
       <c r="X61" s="56"/>
@@ -12104,7 +12200,7 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ61" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12421,7 +12517,9 @@
       <c r="T65" s="56">
         <v>25.15</v>
       </c>
-      <c r="U65" s="56"/>
+      <c r="U65" s="56">
+        <v>26.4</v>
+      </c>
       <c r="V65" s="56"/>
       <c r="W65" s="56"/>
       <c r="X65" s="56"/>
@@ -12444,7 +12542,7 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ65" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12613,7 +12711,9 @@
       <c r="T67" s="56">
         <v>26.35</v>
       </c>
-      <c r="U67" s="56"/>
+      <c r="U67" s="56">
+        <v>27.3</v>
+      </c>
       <c r="V67" s="56"/>
       <c r="W67" s="56"/>
       <c r="X67" s="56"/>
@@ -12636,7 +12736,7 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ67" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12710,7 +12810,9 @@
       <c r="T68" s="56">
         <v>25.45</v>
       </c>
-      <c r="U68" s="56"/>
+      <c r="U68" s="56">
+        <v>26.35</v>
+      </c>
       <c r="V68" s="56"/>
       <c r="W68" s="56"/>
       <c r="X68" s="56"/>
@@ -12733,7 +12835,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12904,7 +13006,9 @@
       <c r="T70" s="56">
         <v>27.166666666666671</v>
       </c>
-      <c r="U70" s="56"/>
+      <c r="U70" s="56">
+        <v>26.833333333333329</v>
+      </c>
       <c r="V70" s="56"/>
       <c r="W70" s="56"/>
       <c r="X70" s="56"/>
@@ -12927,7 +13031,7 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ70" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13096,7 +13200,9 @@
       <c r="T72" s="56">
         <v>25.75</v>
       </c>
-      <c r="U72" s="56"/>
+      <c r="U72" s="56">
+        <v>25.75</v>
+      </c>
       <c r="V72" s="56"/>
       <c r="W72" s="56"/>
       <c r="X72" s="56"/>
@@ -13119,7 +13225,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13192,8 +13298,12 @@
       <c r="S73" s="56">
         <v>19.3</v>
       </c>
-      <c r="T73" s="56"/>
-      <c r="U73" s="56"/>
+      <c r="T73" s="56">
+        <v>20.85</v>
+      </c>
+      <c r="U73" s="56">
+        <v>21.45</v>
+      </c>
       <c r="V73" s="56"/>
       <c r="W73" s="56"/>
       <c r="X73" s="56"/>
@@ -13216,7 +13326,7 @@
       <c r="AO73" s="56"/>
       <c r="AP73" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ73" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13292,7 +13402,9 @@
       <c r="T74" s="56">
         <v>15.06666666666667</v>
       </c>
-      <c r="U74" s="56"/>
+      <c r="U74" s="56">
+        <v>17.06666666666667</v>
+      </c>
       <c r="V74" s="56"/>
       <c r="W74" s="56"/>
       <c r="X74" s="56"/>
@@ -13315,7 +13427,7 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ74" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13391,7 +13503,9 @@
       <c r="T75" s="56">
         <v>20.399999999999999</v>
       </c>
-      <c r="U75" s="56"/>
+      <c r="U75" s="56">
+        <v>22.3</v>
+      </c>
       <c r="V75" s="56"/>
       <c r="W75" s="56"/>
       <c r="X75" s="56"/>
@@ -13414,7 +13528,7 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ75" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13490,7 +13604,9 @@
       <c r="T76" s="56">
         <v>23.86666666666666</v>
       </c>
-      <c r="U76" s="56"/>
+      <c r="U76" s="56">
+        <v>25.2</v>
+      </c>
       <c r="V76" s="56"/>
       <c r="W76" s="56"/>
       <c r="X76" s="56"/>
@@ -13513,7 +13629,7 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ76" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13589,7 +13705,9 @@
       <c r="T77" s="56">
         <v>30</v>
       </c>
-      <c r="U77" s="56"/>
+      <c r="U77" s="56">
+        <v>32.4</v>
+      </c>
       <c r="V77" s="56"/>
       <c r="W77" s="56"/>
       <c r="X77" s="56"/>
@@ -13612,7 +13730,7 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ77" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13876,7 +13994,9 @@
       <c r="T80" s="56">
         <v>25.4</v>
       </c>
-      <c r="U80" s="56"/>
+      <c r="U80" s="56">
+        <v>25.25</v>
+      </c>
       <c r="V80" s="56"/>
       <c r="W80" s="56"/>
       <c r="X80" s="56"/>
@@ -13899,7 +14019,7 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ80" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13975,7 +14095,9 @@
       <c r="T81" s="56">
         <v>27.06666666666667</v>
       </c>
-      <c r="U81" s="56"/>
+      <c r="U81" s="56">
+        <v>25.4</v>
+      </c>
       <c r="V81" s="56"/>
       <c r="W81" s="56"/>
       <c r="X81" s="56"/>
@@ -13998,7 +14120,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14327,7 +14449,9 @@
       <c r="T85" s="56">
         <v>29.55</v>
       </c>
-      <c r="U85" s="56"/>
+      <c r="U85" s="56">
+        <v>29.75</v>
+      </c>
       <c r="V85" s="56"/>
       <c r="W85" s="56"/>
       <c r="X85" s="56"/>
@@ -14350,7 +14474,7 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ85" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14426,7 +14550,9 @@
       <c r="T86" s="56">
         <v>32.849999999999987</v>
       </c>
-      <c r="U86" s="56"/>
+      <c r="U86" s="56">
+        <v>32.650000000000013</v>
+      </c>
       <c r="V86" s="56"/>
       <c r="W86" s="56"/>
       <c r="X86" s="56"/>
@@ -14449,7 +14575,7 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ86" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14525,7 +14651,9 @@
       <c r="T87" s="56">
         <v>31.05</v>
       </c>
-      <c r="U87" s="56"/>
+      <c r="U87" s="56">
+        <v>30.6</v>
+      </c>
       <c r="V87" s="56"/>
       <c r="W87" s="56"/>
       <c r="X87" s="56"/>
@@ -14548,7 +14676,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14620,7 +14748,9 @@
         <v>31.05</v>
       </c>
       <c r="T88" s="56"/>
-      <c r="U88" s="56"/>
+      <c r="U88" s="56">
+        <v>34.950000000000003</v>
+      </c>
       <c r="V88" s="56"/>
       <c r="W88" s="56"/>
       <c r="X88" s="56"/>
@@ -14643,7 +14773,7 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ88" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14713,9 +14843,15 @@
       <c r="R89" s="56">
         <v>33.85</v>
       </c>
-      <c r="S89" s="56"/>
-      <c r="T89" s="56"/>
-      <c r="U89" s="56"/>
+      <c r="S89" s="56">
+        <v>32.049999999999997</v>
+      </c>
+      <c r="T89" s="56">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="U89" s="56">
+        <v>32.1</v>
+      </c>
       <c r="V89" s="56"/>
       <c r="W89" s="56"/>
       <c r="X89" s="56"/>
@@ -14738,7 +14874,7 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ89" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14814,7 +14950,9 @@
       <c r="T90" s="56">
         <v>16.95</v>
       </c>
-      <c r="U90" s="56"/>
+      <c r="U90" s="56">
+        <v>18</v>
+      </c>
       <c r="V90" s="56"/>
       <c r="W90" s="56"/>
       <c r="X90" s="56"/>
@@ -14837,7 +14975,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15012,7 +15150,9 @@
       <c r="T92" s="56">
         <v>17.100000000000001</v>
       </c>
-      <c r="U92" s="56"/>
+      <c r="U92" s="56">
+        <v>18</v>
+      </c>
       <c r="V92" s="56"/>
       <c r="W92" s="56"/>
       <c r="X92" s="56"/>
@@ -15035,7 +15175,7 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ92" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15111,7 +15251,9 @@
       <c r="T93" s="56">
         <v>13.75</v>
       </c>
-      <c r="U93" s="56"/>
+      <c r="U93" s="56">
+        <v>15.45</v>
+      </c>
       <c r="V93" s="56"/>
       <c r="W93" s="56"/>
       <c r="X93" s="56"/>
@@ -15134,7 +15276,7 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ93" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15368,7 +15510,9 @@
       <c r="T96" s="56">
         <v>12.3</v>
       </c>
-      <c r="U96" s="56"/>
+      <c r="U96" s="56">
+        <v>13.85</v>
+      </c>
       <c r="V96" s="56"/>
       <c r="W96" s="56"/>
       <c r="X96" s="56"/>
@@ -15391,7 +15535,7 @@
       <c r="AO96" s="56"/>
       <c r="AP96" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ96" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15463,7 +15607,9 @@
       <c r="T97" s="56">
         <v>13.03333333333333</v>
       </c>
-      <c r="U97" s="56"/>
+      <c r="U97" s="56">
+        <v>14.266666666666669</v>
+      </c>
       <c r="V97" s="56"/>
       <c r="W97" s="56"/>
       <c r="X97" s="56"/>
@@ -15486,7 +15632,7 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ97" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15556,7 +15702,9 @@
       <c r="T98" s="56">
         <v>16.466666666666669</v>
       </c>
-      <c r="U98" s="56"/>
+      <c r="U98" s="56">
+        <v>15.9</v>
+      </c>
       <c r="V98" s="56"/>
       <c r="W98" s="56"/>
       <c r="X98" s="56"/>
@@ -15579,7 +15727,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15746,7 +15894,9 @@
       <c r="T100" s="56">
         <v>12.53333333333333</v>
       </c>
-      <c r="U100" s="56"/>
+      <c r="U100" s="56">
+        <v>13.06666666666667</v>
+      </c>
       <c r="V100" s="56"/>
       <c r="W100" s="56"/>
       <c r="X100" s="56"/>
@@ -15769,7 +15919,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15997,7 +16147,9 @@
       <c r="T103" s="56">
         <v>18.266666666666669</v>
       </c>
-      <c r="U103" s="56"/>
+      <c r="U103" s="56">
+        <v>17.600000000000001</v>
+      </c>
       <c r="V103" s="56"/>
       <c r="W103" s="56"/>
       <c r="X103" s="56"/>
@@ -16020,7 +16172,7 @@
       <c r="AO103" s="56"/>
       <c r="AP103" s="58">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ103" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16262,7 +16414,9 @@
       <c r="T106" s="56">
         <v>13</v>
       </c>
-      <c r="U106" s="56"/>
+      <c r="U106" s="56">
+        <v>13.7</v>
+      </c>
       <c r="V106" s="56"/>
       <c r="W106" s="56"/>
       <c r="X106" s="56"/>
@@ -16285,7 +16439,7 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ106" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16361,7 +16515,9 @@
       <c r="T107" s="56">
         <v>14.25</v>
       </c>
-      <c r="U107" s="56"/>
+      <c r="U107" s="56">
+        <v>15.25</v>
+      </c>
       <c r="V107" s="56"/>
       <c r="W107" s="56"/>
       <c r="X107" s="56"/>
@@ -16384,7 +16540,7 @@
       <c r="AO107" s="56"/>
       <c r="AP107" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ107" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16460,7 +16616,9 @@
       <c r="T108" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="U108" s="56"/>
+      <c r="U108" s="56">
+        <v>18</v>
+      </c>
       <c r="V108" s="56"/>
       <c r="W108" s="56"/>
       <c r="X108" s="56"/>
@@ -16483,7 +16641,7 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ108" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16559,7 +16717,9 @@
       <c r="T109" s="56">
         <v>15.4</v>
       </c>
-      <c r="U109" s="56"/>
+      <c r="U109" s="56">
+        <v>16.86666666666666</v>
+      </c>
       <c r="V109" s="56"/>
       <c r="W109" s="56"/>
       <c r="X109" s="56"/>
@@ -16582,7 +16742,7 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ109" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16755,7 +16915,9 @@
       <c r="T111" s="56">
         <v>19.06666666666667</v>
       </c>
-      <c r="U111" s="56"/>
+      <c r="U111" s="56">
+        <v>19.666666666666671</v>
+      </c>
       <c r="V111" s="56"/>
       <c r="W111" s="56"/>
       <c r="X111" s="56"/>
@@ -16778,7 +16940,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16945,7 +17107,9 @@
       <c r="T113" s="56">
         <v>26.8</v>
       </c>
-      <c r="U113" s="56"/>
+      <c r="U113" s="56">
+        <v>27.1</v>
+      </c>
       <c r="V113" s="56"/>
       <c r="W113" s="56"/>
       <c r="X113" s="56"/>
@@ -16968,7 +17132,7 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ113" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17044,7 +17208,9 @@
       <c r="T114" s="56">
         <v>19.06666666666667</v>
       </c>
-      <c r="U114" s="56"/>
+      <c r="U114" s="56">
+        <v>19.733333333333331</v>
+      </c>
       <c r="V114" s="56"/>
       <c r="W114" s="56"/>
       <c r="X114" s="56"/>
@@ -17067,7 +17233,7 @@
       <c r="AO114" s="56"/>
       <c r="AP114" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ114" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17143,7 +17309,9 @@
       <c r="T115" s="56">
         <v>27.13333333333334</v>
       </c>
-      <c r="U115" s="56"/>
+      <c r="U115" s="56">
+        <v>27</v>
+      </c>
       <c r="V115" s="56"/>
       <c r="W115" s="56"/>
       <c r="X115" s="56"/>
@@ -17166,7 +17334,7 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ115" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17341,7 +17509,9 @@
       <c r="T117" s="56">
         <v>24.333333333333329</v>
       </c>
-      <c r="U117" s="56"/>
+      <c r="U117" s="56">
+        <v>23.533333333333331</v>
+      </c>
       <c r="V117" s="56"/>
       <c r="W117" s="56"/>
       <c r="X117" s="56"/>
@@ -17364,7 +17534,7 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ117" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17429,8 +17599,12 @@
       <c r="S118" s="56">
         <v>23.666666666666671</v>
       </c>
-      <c r="T118" s="56"/>
-      <c r="U118" s="56"/>
+      <c r="T118" s="56">
+        <v>28.2</v>
+      </c>
+      <c r="U118" s="56">
+        <v>27.93333333333333</v>
+      </c>
       <c r="V118" s="56"/>
       <c r="W118" s="56"/>
       <c r="X118" s="56"/>
@@ -17453,7 +17627,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17608,7 +17782,9 @@
       <c r="T120" s="56">
         <v>12.46666666666667</v>
       </c>
-      <c r="U120" s="56"/>
+      <c r="U120" s="56">
+        <v>13.06666666666667</v>
+      </c>
       <c r="V120" s="56"/>
       <c r="W120" s="56"/>
       <c r="X120" s="56"/>
@@ -17631,7 +17807,7 @@
       <c r="AO120" s="56"/>
       <c r="AP120" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ120" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17956,7 +18132,9 @@
       <c r="T124" s="56">
         <v>11.93333333333333</v>
       </c>
-      <c r="U124" s="56"/>
+      <c r="U124" s="56">
+        <v>11.733333333333331</v>
+      </c>
       <c r="V124" s="56"/>
       <c r="W124" s="56"/>
       <c r="X124" s="56"/>
@@ -17979,7 +18157,7 @@
       <c r="AO124" s="56"/>
       <c r="AP124" s="58">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ124" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18292,7 +18470,9 @@
       <c r="T128" s="56">
         <v>15.56666666666667</v>
       </c>
-      <c r="U128" s="56"/>
+      <c r="U128" s="56">
+        <v>15.53333333333333</v>
+      </c>
       <c r="V128" s="56"/>
       <c r="W128" s="56"/>
       <c r="X128" s="56"/>
@@ -18315,7 +18495,7 @@
       <c r="AO128" s="56"/>
       <c r="AP128" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ128" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18391,7 +18571,9 @@
       <c r="T129" s="56">
         <v>18.75</v>
       </c>
-      <c r="U129" s="56"/>
+      <c r="U129" s="56">
+        <v>17.850000000000001</v>
+      </c>
       <c r="V129" s="56"/>
       <c r="W129" s="56"/>
       <c r="X129" s="56"/>
@@ -18414,7 +18596,7 @@
       <c r="AO129" s="56"/>
       <c r="AP129" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ129" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18569,7 +18751,9 @@
       <c r="T131" s="56">
         <v>13.66666666666667</v>
       </c>
-      <c r="U131" s="56"/>
+      <c r="U131" s="56">
+        <v>14.266666666666669</v>
+      </c>
       <c r="V131" s="56"/>
       <c r="W131" s="56"/>
       <c r="X131" s="56"/>
@@ -18592,7 +18776,7 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ131" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18668,7 +18852,9 @@
       <c r="T132" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="U132" s="56"/>
+      <c r="U132" s="56">
+        <v>18.13333333333334</v>
+      </c>
       <c r="V132" s="56"/>
       <c r="W132" s="56"/>
       <c r="X132" s="56"/>
@@ -18691,7 +18877,7 @@
       <c r="AO132" s="56"/>
       <c r="AP132" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ132" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18767,7 +18953,9 @@
       <c r="T133" s="56">
         <v>22.3</v>
       </c>
-      <c r="U133" s="56"/>
+      <c r="U133" s="56">
+        <v>20.45</v>
+      </c>
       <c r="V133" s="56"/>
       <c r="W133" s="56"/>
       <c r="X133" s="56"/>
@@ -18790,7 +18978,7 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ133" s="71" t="str">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
@@ -18860,9 +19048,15 @@
       <c r="R134" s="56">
         <v>11.2</v>
       </c>
-      <c r="S134" s="56"/>
-      <c r="T134" s="56"/>
-      <c r="U134" s="56"/>
+      <c r="S134" s="56">
+        <v>11.53333333333333</v>
+      </c>
+      <c r="T134" s="56">
+        <v>11.6</v>
+      </c>
+      <c r="U134" s="56">
+        <v>12.133333333333329</v>
+      </c>
       <c r="V134" s="56"/>
       <c r="W134" s="56"/>
       <c r="X134" s="56"/>
@@ -18885,7 +19079,7 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ134" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19040,7 +19234,9 @@
       <c r="T136" s="56">
         <v>23.4</v>
       </c>
-      <c r="U136" s="56"/>
+      <c r="U136" s="56">
+        <v>22.666666666666671</v>
+      </c>
       <c r="V136" s="56"/>
       <c r="W136" s="56"/>
       <c r="X136" s="56"/>
@@ -19063,7 +19259,7 @@
       <c r="AO136" s="56"/>
       <c r="AP136" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ136" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19139,7 +19335,9 @@
       <c r="T137" s="56">
         <v>13.85</v>
       </c>
-      <c r="U137" s="56"/>
+      <c r="U137" s="56">
+        <v>13.3</v>
+      </c>
       <c r="V137" s="56"/>
       <c r="W137" s="56"/>
       <c r="X137" s="56"/>
@@ -19162,7 +19360,7 @@
       <c r="AO137" s="56"/>
       <c r="AP137" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ137" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19238,7 +19436,9 @@
       <c r="T138" s="56">
         <v>16.8</v>
       </c>
-      <c r="U138" s="56"/>
+      <c r="U138" s="56">
+        <v>15.85</v>
+      </c>
       <c r="V138" s="56"/>
       <c r="W138" s="56"/>
       <c r="X138" s="56"/>
@@ -19261,7 +19461,7 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ138" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19337,7 +19537,9 @@
       <c r="T139" s="56">
         <v>13.866666666666671</v>
       </c>
-      <c r="U139" s="56"/>
+      <c r="U139" s="56">
+        <v>12.733333333333331</v>
+      </c>
       <c r="V139" s="56"/>
       <c r="W139" s="56"/>
       <c r="X139" s="56"/>
@@ -19360,7 +19562,7 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ139" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19434,7 +19636,9 @@
       <c r="T140" s="56">
         <v>11.5</v>
       </c>
-      <c r="U140" s="56"/>
+      <c r="U140" s="56">
+        <v>11.4</v>
+      </c>
       <c r="V140" s="56"/>
       <c r="W140" s="56"/>
       <c r="X140" s="56"/>
@@ -19457,7 +19661,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19533,7 +19737,9 @@
       <c r="T141" s="56">
         <v>28.333333333333329</v>
       </c>
-      <c r="U141" s="56"/>
+      <c r="U141" s="56">
+        <v>27.8</v>
+      </c>
       <c r="V141" s="56"/>
       <c r="W141" s="56"/>
       <c r="X141" s="56"/>
@@ -19556,7 +19762,7 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ141" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19632,7 +19838,9 @@
       <c r="T142" s="56">
         <v>15.33333333333333</v>
       </c>
-      <c r="U142" s="56"/>
+      <c r="U142" s="56">
+        <v>14.8</v>
+      </c>
       <c r="V142" s="56"/>
       <c r="W142" s="56"/>
       <c r="X142" s="56"/>
@@ -19655,7 +19863,7 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ142" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19731,7 +19939,9 @@
       <c r="T143" s="56">
         <v>18</v>
       </c>
-      <c r="U143" s="56"/>
+      <c r="U143" s="56">
+        <v>19.8</v>
+      </c>
       <c r="V143" s="56"/>
       <c r="W143" s="56"/>
       <c r="X143" s="56"/>
@@ -19754,7 +19964,7 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ143" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19827,8 +20037,12 @@
       <c r="S144" s="56">
         <v>28.333333333333329</v>
       </c>
-      <c r="T144" s="56"/>
-      <c r="U144" s="56"/>
+      <c r="T144" s="56">
+        <v>31.266666666666669</v>
+      </c>
+      <c r="U144" s="56">
+        <v>30.666666666666671</v>
+      </c>
       <c r="V144" s="56"/>
       <c r="W144" s="56"/>
       <c r="X144" s="56"/>
@@ -19851,7 +20065,7 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ144" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19927,7 +20141,9 @@
       <c r="T145" s="56">
         <v>24.266666666666669</v>
       </c>
-      <c r="U145" s="56"/>
+      <c r="U145" s="56">
+        <v>25.666666666666671</v>
+      </c>
       <c r="V145" s="56"/>
       <c r="W145" s="56"/>
       <c r="X145" s="56"/>
@@ -19950,7 +20166,7 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ145" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20024,7 +20240,9 @@
       <c r="T146" s="56">
         <v>29.8</v>
       </c>
-      <c r="U146" s="56"/>
+      <c r="U146" s="56">
+        <v>29.86666666666666</v>
+      </c>
       <c r="V146" s="56"/>
       <c r="W146" s="56"/>
       <c r="X146" s="56"/>
@@ -20047,7 +20265,7 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ146" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20123,7 +20341,9 @@
       <c r="T147" s="56">
         <v>22.733333333333331</v>
       </c>
-      <c r="U147" s="56"/>
+      <c r="U147" s="56">
+        <v>22.93333333333333</v>
+      </c>
       <c r="V147" s="56"/>
       <c r="W147" s="56"/>
       <c r="X147" s="56"/>
@@ -20146,7 +20366,7 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ147" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20298,7 +20518,9 @@
       <c r="S149" s="56">
         <v>23.533333333333331</v>
       </c>
-      <c r="T149" s="56"/>
+      <c r="T149" s="56">
+        <v>22.266666666666669</v>
+      </c>
       <c r="U149" s="56"/>
       <c r="V149" s="56"/>
       <c r="W149" s="56"/>
@@ -20322,7 +20544,7 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ149" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20556,7 +20778,9 @@
       <c r="T152" s="56">
         <v>20.350000000000001</v>
       </c>
-      <c r="U152" s="56"/>
+      <c r="U152" s="56">
+        <v>20.350000000000001</v>
+      </c>
       <c r="V152" s="56"/>
       <c r="W152" s="56"/>
       <c r="X152" s="56"/>
@@ -20579,7 +20803,7 @@
       <c r="AO152" s="56"/>
       <c r="AP152" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ152" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20655,7 +20879,9 @@
       <c r="T153" s="56">
         <v>29.4</v>
       </c>
-      <c r="U153" s="56"/>
+      <c r="U153" s="56">
+        <v>29.533333333333331</v>
+      </c>
       <c r="V153" s="56"/>
       <c r="W153" s="56"/>
       <c r="X153" s="56"/>
@@ -20678,7 +20904,7 @@
       <c r="AO153" s="56"/>
       <c r="AP153" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ153" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20923,7 +21149,9 @@
       <c r="S156" s="56">
         <v>26.06666666666667</v>
       </c>
-      <c r="T156" s="56"/>
+      <c r="T156" s="56">
+        <v>29.86666666666666</v>
+      </c>
       <c r="U156" s="56"/>
       <c r="V156" s="56"/>
       <c r="W156" s="56"/>
@@ -20947,7 +21175,7 @@
       <c r="AO156" s="56"/>
       <c r="AP156" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ156" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21019,7 +21247,9 @@
       <c r="T157" s="56">
         <v>20.266666666666669</v>
       </c>
-      <c r="U157" s="56"/>
+      <c r="U157" s="56">
+        <v>19.93333333333333</v>
+      </c>
       <c r="V157" s="56"/>
       <c r="W157" s="56"/>
       <c r="X157" s="56"/>
@@ -21042,7 +21272,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21118,7 +21348,9 @@
       <c r="T158" s="56">
         <v>27.466666666666669</v>
       </c>
-      <c r="U158" s="56"/>
+      <c r="U158" s="56">
+        <v>26.2</v>
+      </c>
       <c r="V158" s="56"/>
       <c r="W158" s="56"/>
       <c r="X158" s="56"/>
@@ -21141,7 +21373,7 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ158" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21298,9 +21530,15 @@
       <c r="R160" s="56">
         <v>30.13333333333334</v>
       </c>
-      <c r="S160" s="56"/>
-      <c r="T160" s="56"/>
-      <c r="U160" s="56"/>
+      <c r="S160" s="56">
+        <v>26.666666666666671</v>
+      </c>
+      <c r="T160" s="56">
+        <v>28.266666666666669</v>
+      </c>
+      <c r="U160" s="56">
+        <v>29.2</v>
+      </c>
       <c r="V160" s="56"/>
       <c r="W160" s="56"/>
       <c r="X160" s="56"/>
@@ -21323,7 +21561,7 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ160" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21399,7 +21637,9 @@
       <c r="T161" s="56">
         <v>21.466666666666669</v>
       </c>
-      <c r="U161" s="56"/>
+      <c r="U161" s="56">
+        <v>21.133333333333329</v>
+      </c>
       <c r="V161" s="56"/>
       <c r="W161" s="56"/>
       <c r="X161" s="56"/>
@@ -21422,7 +21662,7 @@
       <c r="AO161" s="56"/>
       <c r="AP161" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ161" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21498,7 +21738,9 @@
       <c r="T162" s="56">
         <v>24.9</v>
       </c>
-      <c r="U162" s="56"/>
+      <c r="U162" s="56">
+        <v>24.8</v>
+      </c>
       <c r="V162" s="56"/>
       <c r="W162" s="56"/>
       <c r="X162" s="56"/>
@@ -21521,7 +21763,7 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ162" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21670,9 +21912,15 @@
       <c r="R164" s="56">
         <v>16.466666666666669</v>
       </c>
-      <c r="S164" s="56"/>
-      <c r="T164" s="56"/>
-      <c r="U164" s="56"/>
+      <c r="S164" s="56">
+        <v>14.53333333333333</v>
+      </c>
+      <c r="T164" s="56">
+        <v>14.93333333333333</v>
+      </c>
+      <c r="U164" s="56">
+        <v>14.8</v>
+      </c>
       <c r="V164" s="56"/>
       <c r="W164" s="56"/>
       <c r="X164" s="56"/>
@@ -21695,7 +21943,7 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AQ164" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21767,7 +22015,9 @@
       <c r="T165" s="56">
         <v>19.93333333333333</v>
       </c>
-      <c r="U165" s="56"/>
+      <c r="U165" s="56">
+        <v>20.866666666666671</v>
+      </c>
       <c r="V165" s="56"/>
       <c r="W165" s="56"/>
       <c r="X165" s="56"/>
@@ -21790,7 +22040,7 @@
       <c r="AO165" s="56"/>
       <c r="AP165" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ165" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21866,7 +22116,9 @@
       <c r="T166" s="56">
         <v>28.4</v>
       </c>
-      <c r="U166" s="56"/>
+      <c r="U166" s="56">
+        <v>28</v>
+      </c>
       <c r="V166" s="56"/>
       <c r="W166" s="56"/>
       <c r="X166" s="56"/>
@@ -21889,7 +22141,7 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ166" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21965,7 +22217,9 @@
       <c r="T167" s="56">
         <v>7.75</v>
       </c>
-      <c r="U167" s="56"/>
+      <c r="U167" s="56">
+        <v>7.75</v>
+      </c>
       <c r="V167" s="56"/>
       <c r="W167" s="56"/>
       <c r="X167" s="56"/>
@@ -21988,7 +22242,7 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ167" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22155,9 +22409,11 @@
         <v>19.266666666666669</v>
       </c>
       <c r="T169" s="56">
-        <v>22.1</v>
-      </c>
-      <c r="U169" s="56"/>
+        <v>21.86666666666666</v>
+      </c>
+      <c r="U169" s="56">
+        <v>19.866666666666671</v>
+      </c>
       <c r="V169" s="56"/>
       <c r="W169" s="56"/>
       <c r="X169" s="56"/>
@@ -22180,7 +22436,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22252,7 +22508,9 @@
       <c r="T170" s="56">
         <v>26.2</v>
       </c>
-      <c r="U170" s="56"/>
+      <c r="U170" s="56">
+        <v>25.35</v>
+      </c>
       <c r="V170" s="56"/>
       <c r="W170" s="56"/>
       <c r="X170" s="56"/>
@@ -22275,7 +22533,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22351,7 +22609,9 @@
       <c r="T171" s="56">
         <v>25.8</v>
       </c>
-      <c r="U171" s="56"/>
+      <c r="U171" s="56">
+        <v>24.7</v>
+      </c>
       <c r="V171" s="56"/>
       <c r="W171" s="56"/>
       <c r="X171" s="56"/>
@@ -22374,7 +22634,7 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ171" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22448,7 +22708,9 @@
       <c r="T172" s="56">
         <v>13.53333333333333</v>
       </c>
-      <c r="U172" s="56"/>
+      <c r="U172" s="56">
+        <v>15.4</v>
+      </c>
       <c r="V172" s="56"/>
       <c r="W172" s="56"/>
       <c r="X172" s="56"/>
@@ -22471,7 +22733,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22540,8 +22802,12 @@
       <c r="S173" s="56">
         <v>25</v>
       </c>
-      <c r="T173" s="56"/>
-      <c r="U173" s="56"/>
+      <c r="T173" s="56">
+        <v>24.666666666666671</v>
+      </c>
+      <c r="U173" s="56">
+        <v>24.166666666666671</v>
+      </c>
       <c r="V173" s="56"/>
       <c r="W173" s="56"/>
       <c r="X173" s="56"/>
@@ -22564,7 +22830,7 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ173" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22887,7 +23153,9 @@
       </c>
       <c r="S177" s="56"/>
       <c r="T177" s="56"/>
-      <c r="U177" s="56"/>
+      <c r="U177" s="56">
+        <v>18.350000000000001</v>
+      </c>
       <c r="V177" s="56"/>
       <c r="W177" s="56"/>
       <c r="X177" s="56"/>
@@ -22910,7 +23178,7 @@
       <c r="AO177" s="56"/>
       <c r="AP177" s="58">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ177" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23065,7 +23333,9 @@
       <c r="T179" s="56">
         <v>31.06666666666667</v>
       </c>
-      <c r="U179" s="56"/>
+      <c r="U179" s="56">
+        <v>31.466666666666669</v>
+      </c>
       <c r="V179" s="56"/>
       <c r="W179" s="56"/>
       <c r="X179" s="56"/>
@@ -23088,7 +23358,7 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ179" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23322,7 +23592,9 @@
       <c r="T182" s="56">
         <v>27.6</v>
       </c>
-      <c r="U182" s="56"/>
+      <c r="U182" s="56">
+        <v>27.93333333333333</v>
+      </c>
       <c r="V182" s="56"/>
       <c r="W182" s="56"/>
       <c r="X182" s="56"/>
@@ -23345,7 +23617,7 @@
       <c r="AO182" s="56"/>
       <c r="AP182" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ182" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23678,7 +23950,9 @@
       <c r="T186" s="56">
         <v>18.13333333333334</v>
       </c>
-      <c r="U186" s="56"/>
+      <c r="U186" s="56">
+        <v>19</v>
+      </c>
       <c r="V186" s="56"/>
       <c r="W186" s="56"/>
       <c r="X186" s="56"/>
@@ -23701,7 +23975,7 @@
       <c r="AO186" s="56"/>
       <c r="AP186" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ186" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23771,7 +24045,9 @@
       <c r="T187" s="56">
         <v>32.93333333333333</v>
       </c>
-      <c r="U187" s="56"/>
+      <c r="U187" s="56">
+        <v>32</v>
+      </c>
       <c r="V187" s="56"/>
       <c r="W187" s="56"/>
       <c r="X187" s="56"/>
@@ -23794,7 +24070,7 @@
       <c r="AO187" s="56"/>
       <c r="AP187" s="58">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ187" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23870,7 +24146,9 @@
       <c r="T188" s="56">
         <v>32.066666666666663</v>
       </c>
-      <c r="U188" s="56"/>
+      <c r="U188" s="56">
+        <v>30.666666666666671</v>
+      </c>
       <c r="V188" s="56"/>
       <c r="W188" s="56"/>
       <c r="X188" s="56"/>
@@ -23893,7 +24171,7 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ188" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23966,8 +24244,12 @@
       <c r="S189" s="56">
         <v>17.25</v>
       </c>
-      <c r="T189" s="56"/>
-      <c r="U189" s="56"/>
+      <c r="T189" s="56">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="U189" s="56">
+        <v>20.85</v>
+      </c>
       <c r="V189" s="56"/>
       <c r="W189" s="56"/>
       <c r="X189" s="56"/>
@@ -23990,7 +24272,7 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ189" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24066,7 +24348,9 @@
       <c r="T190" s="56">
         <v>26.533333333333331</v>
       </c>
-      <c r="U190" s="56"/>
+      <c r="U190" s="56">
+        <v>27.13333333333334</v>
+      </c>
       <c r="V190" s="56"/>
       <c r="W190" s="56"/>
       <c r="X190" s="56"/>
@@ -24089,7 +24373,7 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ190" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24163,7 +24447,9 @@
       <c r="T191" s="56">
         <v>26.2</v>
       </c>
-      <c r="U191" s="56"/>
+      <c r="U191" s="56">
+        <v>27.9</v>
+      </c>
       <c r="V191" s="56"/>
       <c r="W191" s="56"/>
       <c r="X191" s="56"/>
@@ -24186,7 +24472,7 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ191" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24262,7 +24548,9 @@
       <c r="T192" s="56">
         <v>20.8</v>
       </c>
-      <c r="U192" s="56"/>
+      <c r="U192" s="56">
+        <v>22.13333333333334</v>
+      </c>
       <c r="V192" s="56"/>
       <c r="W192" s="56"/>
       <c r="X192" s="56"/>
@@ -24285,7 +24573,7 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ192" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24361,7 +24649,9 @@
       <c r="T193" s="56">
         <v>28.4</v>
       </c>
-      <c r="U193" s="56"/>
+      <c r="U193" s="56">
+        <v>28.8</v>
+      </c>
       <c r="V193" s="56"/>
       <c r="W193" s="56"/>
       <c r="X193" s="56"/>
@@ -24384,7 +24674,7 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ193" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24460,7 +24750,9 @@
       <c r="T194" s="56">
         <v>22.733333333333331</v>
       </c>
-      <c r="U194" s="56"/>
+      <c r="U194" s="56">
+        <v>23.466666666666669</v>
+      </c>
       <c r="V194" s="56"/>
       <c r="W194" s="56"/>
       <c r="X194" s="56"/>
@@ -24483,7 +24775,7 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ194" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24559,7 +24851,9 @@
       <c r="T195" s="56">
         <v>25.6</v>
       </c>
-      <c r="U195" s="56"/>
+      <c r="U195" s="56">
+        <v>26.333333333333329</v>
+      </c>
       <c r="V195" s="56"/>
       <c r="W195" s="56"/>
       <c r="X195" s="56"/>
@@ -24582,7 +24876,7 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ195" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24658,7 +24952,9 @@
       <c r="T196" s="56">
         <v>21.95</v>
       </c>
-      <c r="U196" s="56"/>
+      <c r="U196" s="56">
+        <v>22.65</v>
+      </c>
       <c r="V196" s="56"/>
       <c r="W196" s="56"/>
       <c r="X196" s="56"/>
@@ -24681,7 +24977,7 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ196" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24757,7 +25053,9 @@
       <c r="T197" s="56">
         <v>16.666666666666671</v>
       </c>
-      <c r="U197" s="56"/>
+      <c r="U197" s="56">
+        <v>16.866666666666671</v>
+      </c>
       <c r="V197" s="56"/>
       <c r="W197" s="56"/>
       <c r="X197" s="56"/>
@@ -24780,7 +25078,7 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ197" s="71" t="str">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
@@ -24856,7 +25154,9 @@
       <c r="T198" s="56">
         <v>14.2</v>
       </c>
-      <c r="U198" s="56"/>
+      <c r="U198" s="56">
+        <v>13.85</v>
+      </c>
       <c r="V198" s="56"/>
       <c r="W198" s="56"/>
       <c r="X198" s="56"/>
@@ -24879,7 +25179,7 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ198" s="71" t="str">
         <f t="shared" si="10"/>
@@ -24955,7 +25255,9 @@
       <c r="T199" s="56">
         <v>27.6</v>
       </c>
-      <c r="U199" s="56"/>
+      <c r="U199" s="56">
+        <v>27.4</v>
+      </c>
       <c r="V199" s="56"/>
       <c r="W199" s="56"/>
       <c r="X199" s="56"/>
@@ -24978,7 +25280,7 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ199" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25054,7 +25356,9 @@
       <c r="T200" s="56">
         <v>13.35</v>
       </c>
-      <c r="U200" s="56"/>
+      <c r="U200" s="56">
+        <v>13.05</v>
+      </c>
       <c r="V200" s="56"/>
       <c r="W200" s="56"/>
       <c r="X200" s="56"/>
@@ -25077,7 +25381,7 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ200" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25149,7 +25453,9 @@
       </c>
       <c r="S201" s="56"/>
       <c r="T201" s="56"/>
-      <c r="U201" s="56"/>
+      <c r="U201" s="56">
+        <v>14.33333333333333</v>
+      </c>
       <c r="V201" s="56"/>
       <c r="W201" s="56"/>
       <c r="X201" s="56"/>
@@ -25172,7 +25478,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25244,7 +25550,9 @@
       <c r="T202" s="56">
         <v>13.3</v>
       </c>
-      <c r="U202" s="56"/>
+      <c r="U202" s="56">
+        <v>12.15</v>
+      </c>
       <c r="V202" s="56"/>
       <c r="W202" s="56"/>
       <c r="X202" s="56"/>
@@ -25267,7 +25575,7 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ202" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25343,7 +25651,9 @@
       <c r="T203" s="56">
         <v>14</v>
       </c>
-      <c r="U203" s="56"/>
+      <c r="U203" s="56">
+        <v>14.35</v>
+      </c>
       <c r="V203" s="56"/>
       <c r="W203" s="56"/>
       <c r="X203" s="56"/>
@@ -25366,7 +25676,7 @@
       <c r="AO203" s="56"/>
       <c r="AP203" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ203" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25439,7 +25749,9 @@
       <c r="S204" s="56">
         <v>13.3</v>
       </c>
-      <c r="T204" s="56"/>
+      <c r="T204" s="56">
+        <v>13.45</v>
+      </c>
       <c r="U204" s="56"/>
       <c r="V204" s="56"/>
       <c r="W204" s="56"/>
@@ -25463,7 +25775,7 @@
       <c r="AO204" s="56"/>
       <c r="AP204" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ204" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25632,7 +25944,9 @@
       <c r="T206" s="56">
         <v>13.15</v>
       </c>
-      <c r="U206" s="56"/>
+      <c r="U206" s="56">
+        <v>13.6</v>
+      </c>
       <c r="V206" s="56"/>
       <c r="W206" s="56"/>
       <c r="X206" s="56"/>
@@ -25655,7 +25969,7 @@
       <c r="AO206" s="56"/>
       <c r="AP206" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ206" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25731,7 +26045,9 @@
       <c r="T207" s="56">
         <v>10.9</v>
       </c>
-      <c r="U207" s="56"/>
+      <c r="U207" s="56">
+        <v>10.5</v>
+      </c>
       <c r="V207" s="56"/>
       <c r="W207" s="56"/>
       <c r="X207" s="56"/>
@@ -25754,7 +26070,7 @@
       <c r="AO207" s="56"/>
       <c r="AP207" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ207" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25827,8 +26143,12 @@
       <c r="S208" s="56">
         <v>14.8</v>
       </c>
-      <c r="T208" s="56"/>
-      <c r="U208" s="56"/>
+      <c r="T208" s="56">
+        <v>15.3</v>
+      </c>
+      <c r="U208" s="56">
+        <v>17.399999999999999</v>
+      </c>
       <c r="V208" s="56"/>
       <c r="W208" s="56"/>
       <c r="X208" s="56"/>
@@ -25851,7 +26171,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
